--- a/artfynd/A 42324-2025 artfynd.xlsx
+++ b/artfynd/A 42324-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128804148</v>
       </c>
       <c r="B2" t="n">
-        <v>91432</v>
+        <v>91459</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>128804149</v>
       </c>
       <c r="B3" t="n">
-        <v>56615</v>
+        <v>56642</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>128804151</v>
       </c>
       <c r="B4" t="n">
-        <v>100780</v>
+        <v>100807</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -984,7 +984,7 @@
         <v>128804142</v>
       </c>
       <c r="B5" t="n">
-        <v>75115</v>
+        <v>75142</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1096,7 +1096,7 @@
         <v>128804154</v>
       </c>
       <c r="B6" t="n">
-        <v>95919</v>
+        <v>95946</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>128804146</v>
       </c>
       <c r="B7" t="n">
-        <v>75115</v>
+        <v>75142</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1290,7 +1290,7 @@
         <v>128804143</v>
       </c>
       <c r="B8" t="n">
-        <v>80754</v>
+        <v>80781</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1524,7 +1524,7 @@
         <v>128804147</v>
       </c>
       <c r="B10" t="n">
-        <v>57686</v>
+        <v>57713</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 42324-2025 artfynd.xlsx
+++ b/artfynd/A 42324-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128804148</v>
       </c>
       <c r="B2" t="n">
-        <v>91459</v>
+        <v>91464</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128804149</v>
+        <v>128804151</v>
       </c>
       <c r="B3" t="n">
-        <v>56642</v>
+        <v>100813</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -798,21 +798,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>208257</v>
+        <v>222498</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kopparödla</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Anguis fragilis</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>327487</v>
+        <v>327337</v>
       </c>
       <c r="R3" t="n">
-        <v>6493852</v>
+        <v>6493822</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -884,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128804151</v>
+        <v>128804149</v>
       </c>
       <c r="B4" t="n">
-        <v>100807</v>
+        <v>56642</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222498</v>
+        <v>208257</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Kopparödla</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Anguis fragilis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>327337</v>
+        <v>327487</v>
       </c>
       <c r="R4" t="n">
-        <v>6493822</v>
+        <v>6493852</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -984,7 +984,7 @@
         <v>128804142</v>
       </c>
       <c r="B5" t="n">
-        <v>75142</v>
+        <v>75143</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1096,7 +1096,7 @@
         <v>128804154</v>
       </c>
       <c r="B6" t="n">
-        <v>95946</v>
+        <v>95952</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>128804146</v>
       </c>
       <c r="B7" t="n">
-        <v>75142</v>
+        <v>75143</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1290,7 +1290,7 @@
         <v>128804143</v>
       </c>
       <c r="B8" t="n">
-        <v>80781</v>
+        <v>80785</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 42324-2025 artfynd.xlsx
+++ b/artfynd/A 42324-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128804148</v>
       </c>
       <c r="B2" t="n">
-        <v>91464</v>
+        <v>91469</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>128804151</v>
       </c>
       <c r="B3" t="n">
-        <v>100813</v>
+        <v>100820</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1096,7 +1096,7 @@
         <v>128804154</v>
       </c>
       <c r="B6" t="n">
-        <v>95952</v>
+        <v>95959</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 42324-2025 artfynd.xlsx
+++ b/artfynd/A 42324-2025 artfynd.xlsx
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128804151</v>
+        <v>128804149</v>
       </c>
       <c r="B3" t="n">
-        <v>100820</v>
+        <v>56642</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -798,21 +798,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222498</v>
+        <v>208257</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Kopparödla</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Anguis fragilis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>327337</v>
+        <v>327487</v>
       </c>
       <c r="R3" t="n">
-        <v>6493822</v>
+        <v>6493852</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -884,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128804149</v>
+        <v>128804151</v>
       </c>
       <c r="B4" t="n">
-        <v>56642</v>
+        <v>100820</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>208257</v>
+        <v>222498</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kopparödla</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Anguis fragilis</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>327487</v>
+        <v>327337</v>
       </c>
       <c r="R4" t="n">
-        <v>6493852</v>
+        <v>6493822</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>

--- a/artfynd/A 42324-2025 artfynd.xlsx
+++ b/artfynd/A 42324-2025 artfynd.xlsx
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128804149</v>
+        <v>128804151</v>
       </c>
       <c r="B3" t="n">
-        <v>56642</v>
+        <v>100820</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -798,21 +798,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>208257</v>
+        <v>222498</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kopparödla</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Anguis fragilis</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>327487</v>
+        <v>327337</v>
       </c>
       <c r="R3" t="n">
-        <v>6493852</v>
+        <v>6493822</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -884,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128804151</v>
+        <v>128804149</v>
       </c>
       <c r="B4" t="n">
-        <v>100820</v>
+        <v>56642</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222498</v>
+        <v>208257</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Kopparödla</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Anguis fragilis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>327337</v>
+        <v>327487</v>
       </c>
       <c r="R4" t="n">
-        <v>6493822</v>
+        <v>6493852</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>

--- a/artfynd/A 42324-2025 artfynd.xlsx
+++ b/artfynd/A 42324-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128804148</v>
       </c>
       <c r="B2" t="n">
-        <v>91469</v>
+        <v>91473</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>128804151</v>
       </c>
       <c r="B3" t="n">
-        <v>100820</v>
+        <v>100824</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>128804149</v>
       </c>
       <c r="B4" t="n">
-        <v>56642</v>
+        <v>56645</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -984,7 +984,7 @@
         <v>128804142</v>
       </c>
       <c r="B5" t="n">
-        <v>75143</v>
+        <v>75147</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1096,7 +1096,7 @@
         <v>128804154</v>
       </c>
       <c r="B6" t="n">
-        <v>95959</v>
+        <v>95963</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>128804146</v>
       </c>
       <c r="B7" t="n">
-        <v>75143</v>
+        <v>75147</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1290,7 +1290,7 @@
         <v>128804143</v>
       </c>
       <c r="B8" t="n">
-        <v>80785</v>
+        <v>80789</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1524,7 +1524,7 @@
         <v>128804147</v>
       </c>
       <c r="B10" t="n">
-        <v>57713</v>
+        <v>57717</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 42324-2025 artfynd.xlsx
+++ b/artfynd/A 42324-2025 artfynd.xlsx
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128804151</v>
+        <v>128804149</v>
       </c>
       <c r="B3" t="n">
-        <v>100824</v>
+        <v>56645</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -798,21 +798,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222498</v>
+        <v>208257</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Kopparödla</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Anguis fragilis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>327337</v>
+        <v>327487</v>
       </c>
       <c r="R3" t="n">
-        <v>6493822</v>
+        <v>6493852</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -884,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128804149</v>
+        <v>128804151</v>
       </c>
       <c r="B4" t="n">
-        <v>56645</v>
+        <v>100824</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>208257</v>
+        <v>222498</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kopparödla</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Anguis fragilis</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>327487</v>
+        <v>327337</v>
       </c>
       <c r="R4" t="n">
-        <v>6493852</v>
+        <v>6493822</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>

--- a/artfynd/A 42324-2025 artfynd.xlsx
+++ b/artfynd/A 42324-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128804148</v>
       </c>
       <c r="B2" t="n">
-        <v>91473</v>
+        <v>91478</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128804149</v>
+        <v>128804151</v>
       </c>
       <c r="B3" t="n">
-        <v>56645</v>
+        <v>100831</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -798,21 +798,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>208257</v>
+        <v>222498</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kopparödla</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Anguis fragilis</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>327487</v>
+        <v>327337</v>
       </c>
       <c r="R3" t="n">
-        <v>6493852</v>
+        <v>6493822</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -884,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128804151</v>
+        <v>128804149</v>
       </c>
       <c r="B4" t="n">
-        <v>100824</v>
+        <v>56648</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222498</v>
+        <v>208257</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Kopparödla</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Anguis fragilis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>327337</v>
+        <v>327487</v>
       </c>
       <c r="R4" t="n">
-        <v>6493822</v>
+        <v>6493852</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -984,7 +984,7 @@
         <v>128804142</v>
       </c>
       <c r="B5" t="n">
-        <v>75147</v>
+        <v>75150</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1096,7 +1096,7 @@
         <v>128804154</v>
       </c>
       <c r="B6" t="n">
-        <v>95963</v>
+        <v>95970</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>128804146</v>
       </c>
       <c r="B7" t="n">
-        <v>75147</v>
+        <v>75150</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1290,7 +1290,7 @@
         <v>128804143</v>
       </c>
       <c r="B8" t="n">
-        <v>80789</v>
+        <v>80694</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1524,7 +1524,7 @@
         <v>128804147</v>
       </c>
       <c r="B10" t="n">
-        <v>57717</v>
+        <v>57720</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 42324-2025 artfynd.xlsx
+++ b/artfynd/A 42324-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128804148</v>
       </c>
       <c r="B2" t="n">
-        <v>91485</v>
+        <v>91488</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128804149</v>
+        <v>128804151</v>
       </c>
       <c r="B3" t="n">
-        <v>56648</v>
+        <v>100844</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -798,21 +798,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>208257</v>
+        <v>222498</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kopparödla</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Anguis fragilis</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>327487</v>
+        <v>327337</v>
       </c>
       <c r="R3" t="n">
-        <v>6493852</v>
+        <v>6493822</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -884,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128804151</v>
+        <v>128804149</v>
       </c>
       <c r="B4" t="n">
-        <v>100839</v>
+        <v>56648</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222498</v>
+        <v>208257</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Kopparödla</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Anguis fragilis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>327337</v>
+        <v>327487</v>
       </c>
       <c r="R4" t="n">
-        <v>6493822</v>
+        <v>6493852</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1096,7 +1096,7 @@
         <v>128804154</v>
       </c>
       <c r="B6" t="n">
-        <v>95978</v>
+        <v>95983</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 42324-2025 artfynd.xlsx
+++ b/artfynd/A 42324-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128804148</v>
       </c>
       <c r="B2" t="n">
-        <v>91488</v>
+        <v>91491</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128804151</v>
+        <v>128804149</v>
       </c>
       <c r="B3" t="n">
-        <v>100844</v>
+        <v>56648</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -798,21 +798,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222498</v>
+        <v>208257</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Kopparödla</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Anguis fragilis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>327337</v>
+        <v>327487</v>
       </c>
       <c r="R3" t="n">
-        <v>6493822</v>
+        <v>6493852</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -884,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128804149</v>
+        <v>128804151</v>
       </c>
       <c r="B4" t="n">
-        <v>56648</v>
+        <v>100847</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>208257</v>
+        <v>222498</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kopparödla</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Anguis fragilis</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>327487</v>
+        <v>327337</v>
       </c>
       <c r="R4" t="n">
-        <v>6493852</v>
+        <v>6493822</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1096,7 +1096,7 @@
         <v>128804154</v>
       </c>
       <c r="B6" t="n">
-        <v>95983</v>
+        <v>95986</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1290,7 +1290,7 @@
         <v>128804143</v>
       </c>
       <c r="B8" t="n">
-        <v>80699</v>
+        <v>80700</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 42324-2025 artfynd.xlsx
+++ b/artfynd/A 42324-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128804148</v>
       </c>
       <c r="B2" t="n">
-        <v>91491</v>
+        <v>91497</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>128804149</v>
       </c>
       <c r="B3" t="n">
-        <v>56648</v>
+        <v>56650</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>128804151</v>
       </c>
       <c r="B4" t="n">
-        <v>100847</v>
+        <v>100857</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -984,7 +984,7 @@
         <v>128804142</v>
       </c>
       <c r="B5" t="n">
-        <v>75155</v>
+        <v>75157</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1096,7 +1096,7 @@
         <v>128804154</v>
       </c>
       <c r="B6" t="n">
-        <v>95986</v>
+        <v>95996</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>128804146</v>
       </c>
       <c r="B7" t="n">
-        <v>75155</v>
+        <v>75157</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1290,7 +1290,7 @@
         <v>128804143</v>
       </c>
       <c r="B8" t="n">
-        <v>80700</v>
+        <v>80704</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1524,7 +1524,7 @@
         <v>128804147</v>
       </c>
       <c r="B10" t="n">
-        <v>57720</v>
+        <v>57722</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 42324-2025 artfynd.xlsx
+++ b/artfynd/A 42324-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128804148</v>
       </c>
       <c r="B2" t="n">
-        <v>91497</v>
+        <v>91504</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>128804151</v>
       </c>
       <c r="B4" t="n">
-        <v>100857</v>
+        <v>100864</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1096,7 +1096,7 @@
         <v>128804154</v>
       </c>
       <c r="B6" t="n">
-        <v>95996</v>
+        <v>96003</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 42324-2025 artfynd.xlsx
+++ b/artfynd/A 42324-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128804148</v>
       </c>
       <c r="B2" t="n">
-        <v>91504</v>
+        <v>91506</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>128804149</v>
       </c>
       <c r="B3" t="n">
-        <v>56650</v>
+        <v>56652</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>128804151</v>
       </c>
       <c r="B4" t="n">
-        <v>100864</v>
+        <v>100866</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -984,7 +984,7 @@
         <v>128804142</v>
       </c>
       <c r="B5" t="n">
-        <v>75157</v>
+        <v>75159</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1096,7 +1096,7 @@
         <v>128804154</v>
       </c>
       <c r="B6" t="n">
-        <v>96003</v>
+        <v>96005</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>128804146</v>
       </c>
       <c r="B7" t="n">
-        <v>75157</v>
+        <v>75159</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1290,7 +1290,7 @@
         <v>128804143</v>
       </c>
       <c r="B8" t="n">
-        <v>80704</v>
+        <v>80706</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1524,7 +1524,7 @@
         <v>128804147</v>
       </c>
       <c r="B10" t="n">
-        <v>57722</v>
+        <v>57724</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 42324-2025 artfynd.xlsx
+++ b/artfynd/A 42324-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128804148</v>
       </c>
       <c r="B2" t="n">
-        <v>91506</v>
+        <v>91504</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128804149</v>
+        <v>128804151</v>
       </c>
       <c r="B3" t="n">
-        <v>56652</v>
+        <v>100892</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -798,21 +798,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>208257</v>
+        <v>222498</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kopparödla</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Anguis fragilis</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>327487</v>
+        <v>327337</v>
       </c>
       <c r="R3" t="n">
-        <v>6493852</v>
+        <v>6493822</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -884,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128804151</v>
+        <v>128804149</v>
       </c>
       <c r="B4" t="n">
-        <v>100866</v>
+        <v>56652</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222498</v>
+        <v>208257</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Kopparödla</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Anguis fragilis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>327337</v>
+        <v>327487</v>
       </c>
       <c r="R4" t="n">
-        <v>6493822</v>
+        <v>6493852</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1096,7 +1096,7 @@
         <v>128804154</v>
       </c>
       <c r="B6" t="n">
-        <v>96005</v>
+        <v>96031</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 42324-2025 artfynd.xlsx
+++ b/artfynd/A 42324-2025 artfynd.xlsx
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128804151</v>
+        <v>128804149</v>
       </c>
       <c r="B3" t="n">
-        <v>100892</v>
+        <v>56652</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -798,21 +798,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222498</v>
+        <v>208257</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Kopparödla</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Anguis fragilis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>327337</v>
+        <v>327487</v>
       </c>
       <c r="R3" t="n">
-        <v>6493822</v>
+        <v>6493852</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -884,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128804149</v>
+        <v>128804151</v>
       </c>
       <c r="B4" t="n">
-        <v>56652</v>
+        <v>100894</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>208257</v>
+        <v>222498</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kopparödla</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Anguis fragilis</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>327487</v>
+        <v>327337</v>
       </c>
       <c r="R4" t="n">
-        <v>6493852</v>
+        <v>6493822</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1096,7 +1096,7 @@
         <v>128804154</v>
       </c>
       <c r="B6" t="n">
-        <v>96031</v>
+        <v>96032</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 42324-2025 artfynd.xlsx
+++ b/artfynd/A 42324-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128804148</v>
+        <v>128804154</v>
       </c>
       <c r="B2" t="n">
-        <v>91504</v>
+        <v>96439</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5447</v>
+        <v>2666</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Grov fjädermossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Exsertotheca crispa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>327518</v>
+        <v>327320</v>
       </c>
       <c r="R2" t="n">
-        <v>6493835</v>
+        <v>6493812</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -756,21 +756,6 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -787,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128804149</v>
+        <v>128804148</v>
       </c>
       <c r="B3" t="n">
-        <v>56652</v>
+        <v>91872</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -798,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>208257</v>
+        <v>5447</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kopparödla</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Anguis fragilis</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>327487</v>
+        <v>327518</v>
       </c>
       <c r="R3" t="n">
-        <v>6493852</v>
+        <v>6493835</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -868,6 +853,21 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -884,32 +884,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128804151</v>
+        <v>128804142</v>
       </c>
       <c r="B4" t="n">
-        <v>100894</v>
+        <v>75428</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222498</v>
+        <v>6426</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>327337</v>
+        <v>327944</v>
       </c>
       <c r="R4" t="n">
-        <v>6493822</v>
+        <v>6493679</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -965,6 +965,21 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -981,14 +996,14 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128804142</v>
+        <v>128804146</v>
       </c>
       <c r="B5" t="n">
-        <v>75159</v>
+        <v>75428</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -1016,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>327944</v>
+        <v>327622</v>
       </c>
       <c r="R5" t="n">
-        <v>6493679</v>
+        <v>6493786</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1062,21 +1077,6 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1093,10 +1093,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128804154</v>
+        <v>128804147</v>
       </c>
       <c r="B6" t="n">
-        <v>96032</v>
+        <v>57950</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1104,34 +1104,42 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2666</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Grov fjädermossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Exsertotheca crispa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Dyrtorp, Dls</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>327320</v>
+        <v>327609</v>
       </c>
       <c r="R6" t="n">
-        <v>6493812</v>
+        <v>6493822</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1190,10 +1198,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128804146</v>
+        <v>128804141</v>
       </c>
       <c r="B7" t="n">
-        <v>75159</v>
+        <v>4781</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1201,34 +1209,43 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6426</v>
+        <v>102306</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Dyrtorp, Dls</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>327622</v>
+        <v>327944</v>
       </c>
       <c r="R7" t="n">
-        <v>6493786</v>
+        <v>6493679</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1269,8 +1286,24 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1287,10 +1320,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128804143</v>
+        <v>128804145</v>
       </c>
       <c r="B8" t="n">
-        <v>80706</v>
+        <v>4781</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1298,34 +1331,39 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>230185</v>
+        <v>102306</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Dyrtorp, Dls</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>327939</v>
+        <v>327685</v>
       </c>
       <c r="R8" t="n">
-        <v>6493724</v>
+        <v>6493730</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1366,22 +1404,23 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>klibbal</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>Alnus glutinosa</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>Alnus glutinosa</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1399,10 +1438,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128804141</v>
+        <v>128804149</v>
       </c>
       <c r="B9" t="n">
-        <v>4779</v>
+        <v>56876</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1410,43 +1449,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>102306</v>
+        <v>208257</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Kopparödla</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Anguis fragilis</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Dyrtorp, Dls</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>327944</v>
+        <v>327487</v>
       </c>
       <c r="R9" t="n">
-        <v>6493679</v>
+        <v>6493852</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1487,24 +1517,8 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1521,50 +1535,42 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128804147</v>
+        <v>128804151</v>
       </c>
       <c r="B10" t="n">
-        <v>57724</v>
+        <v>101325</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Dyrtorp, Dls</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>327609</v>
+        <v>327337</v>
       </c>
       <c r="R10" t="n">
         <v>6493822</v>
@@ -1626,10 +1632,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128804145</v>
+        <v>128804143</v>
       </c>
       <c r="B11" t="n">
-        <v>4779</v>
+        <v>80992</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1637,39 +1643,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>102306</v>
+        <v>230185</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Dyrtorp, Dls</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>327685</v>
+        <v>327939</v>
       </c>
       <c r="R11" t="n">
-        <v>6493730</v>
+        <v>6493724</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1710,23 +1711,22 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>klibbal</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Alnus glutinosa</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Alnus glutinosa</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>

--- a/artfynd/A 42324-2025 artfynd.xlsx
+++ b/artfynd/A 42324-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AZ11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128804154</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -881,6 +891,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128804148</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -978,6 +993,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128804146</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1083,6 +1103,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128804147</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1201,6 +1226,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128804145</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1298,6 +1328,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128804149</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1395,6 +1430,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128804151</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1507,6 +1547,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128804142</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1629,6 +1674,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128804141</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1741,8 +1791,25 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128804143</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>